--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -23439,29 +23439,11 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23469,7 +23451,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23477,6 +23459,24 @@
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24237,44 +24237,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25049,41 +25049,14 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 -
@@ -25091,7 +25064,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25099,6 +25072,33 @@
 (在售)</t>
         </is>
       </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1304</v>
+        <v>1254</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4493,14 +4493,14 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
         <v>32339200</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>24800</v>
+        <v>25789</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>32339200</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>24800</v>
+        <v>25789</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="E195" s="4" t="n">
-        <v>1856</v>
+        <v>1788</v>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
@@ -13697,14 +13697,14 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
         <v>55297000</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>29794</v>
+        <v>30927</v>
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>55297000</v>
       </c>
       <c r="L195" s="5" t="n">
-        <v>29794</v>
+        <v>30927</v>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
@@ -23663,10 +23663,10 @@
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>C | 1304呎 (3房)
+          <t>C | 1254呎 (3房)
 $3234万
-$24,800/呎
-(26年-08月-20日)</t>
+$25,789/呎
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr"/>
@@ -25321,10 +25321,10 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>B | 1856呎 (4+房)
+          <t>B | 1788呎 (4+房)
 $5530万
-$29,794/呎
-(26年-08月-20日)</t>
+$30,927/呎
+(26年-09月-08日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr"/>
@@ -26686,34 +26686,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -18990,34 +18990,34 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
-        <v>40210600</v>
+        <v>37798000</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>26281</v>
+        <v>24705</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K278" s="5" t="n">
-        <v>37797964</v>
+        <v>37798000</v>
       </c>
       <c r="L278" s="5" t="n">
         <v>24705</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N278" s="3" t="inlineStr">
@@ -25839,12 +25839,12 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -26289,12 +26289,12 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
-$4021万
-$26,281/呎
-(已定价未售)</t>
+$3780万
+$24,705/呎
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1711</v>
+        <v>1625</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3647,14 +3647,14 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
         <v>62964800</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>36800</v>
+        <v>38748</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>62964800</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>36800</v>
+        <v>38748</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J168" s="3" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M168" s="3" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="N168" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12022,7 +12022,7 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -12032,12 +12032,12 @@
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J170" s="3" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M170" s="3" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="N170" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J174" s="3" t="inlineStr">
@@ -12319,12 +12319,12 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M174" s="3" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="N174" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J176" s="3" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M176" s="3" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J178" s="3" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M178" s="3" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="N178" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -12840,12 +12840,12 @@
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J182" s="3" t="inlineStr">
@@ -12855,12 +12855,12 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M182" s="3" t="inlineStr">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="N182" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -13104,12 +13104,12 @@
       </c>
       <c r="H186" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I186" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J186" s="3" t="inlineStr">
@@ -13119,12 +13119,12 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M186" s="3" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="N186" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13358,7 +13358,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -13368,12 +13368,12 @@
       </c>
       <c r="H190" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I190" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J190" s="3" t="inlineStr">
@@ -13383,12 +13383,12 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M190" s="3" t="inlineStr">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="N190" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -13632,12 +13632,12 @@
       </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J194" s="3" t="inlineStr">
@@ -13647,12 +13647,12 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M194" s="3" t="inlineStr">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="N194" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="H198" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I198" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J198" s="3" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M198" s="3" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="N198" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14134,7 +14134,7 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="H202" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I202" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J202" s="3" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M202" s="3" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -14214,12 +14214,12 @@
       </c>
       <c r="H203" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I203" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J203" s="3" t="inlineStr">
@@ -14229,12 +14229,12 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L203" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M203" s="3" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="N203" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14522,7 +14522,7 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I208" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J208" s="3" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M208" s="3" t="inlineStr">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="N208" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="H209" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I209" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J209" s="3" t="inlineStr">
@@ -14617,12 +14617,12 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L209" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M209" s="3" t="inlineStr">
@@ -14632,7 +14632,7 @@
       </c>
       <c r="N209" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -14920,12 +14920,12 @@
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I214" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J214" s="3" t="inlineStr">
@@ -14935,12 +14935,12 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="N214" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14980,7 +14980,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -14990,12 +14990,12 @@
       </c>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I215" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J215" s="3" t="inlineStr">
@@ -15005,12 +15005,12 @@
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="N215" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -15308,12 +15308,12 @@
       </c>
       <c r="H220" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I220" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J220" s="3" t="inlineStr">
@@ -15323,12 +15323,12 @@
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
@@ -15338,7 +15338,7 @@
       </c>
       <c r="N220" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15368,7 +15368,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -15378,12 +15378,12 @@
       </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I221" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J221" s="3" t="inlineStr">
@@ -15393,12 +15393,12 @@
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L221" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M221" s="3" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="N221" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23439,11 +23439,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23451,7 +23469,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23459,24 +23477,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -23487,10 +23487,10 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 1711呎 (4+房)
+          <t>A | 1625呎 (4+房)
 $6296万
-$36,800/呎
-(26年-09月-03日)</t>
+$38,748/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -24237,44 +24237,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24958,7 +24958,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -24978,7 +24978,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -25029,12 +25029,12 @@
       <c r="C5" s="21" t="inlineStr"/>
       <c r="D5" s="21" t="inlineStr"/>
       <c r="E5" s="21" t="inlineStr"/>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
@@ -25049,22 +25049,49 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="24" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25073,45 +25100,18 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>A | 1865呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -25124,12 +25124,12 @@
       </c>
       <c r="D8" s="21" t="inlineStr"/>
       <c r="E8" s="21" t="inlineStr"/>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
@@ -25165,12 +25165,12 @@
       </c>
       <c r="D9" s="21" t="inlineStr"/>
       <c r="E9" s="21" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -25206,12 +25206,12 @@
       </c>
       <c r="D10" s="21" t="inlineStr"/>
       <c r="E10" s="21" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -25247,12 +25247,12 @@
       </c>
       <c r="D11" s="21" t="inlineStr"/>
       <c r="E11" s="21" t="inlineStr"/>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -25288,12 +25288,12 @@
       </c>
       <c r="D12" s="21" t="inlineStr"/>
       <c r="E12" s="21" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -25329,12 +25329,12 @@
       </c>
       <c r="D13" s="21" t="inlineStr"/>
       <c r="E13" s="21" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -25370,12 +25370,12 @@
       </c>
       <c r="D14" s="21" t="inlineStr"/>
       <c r="E14" s="21" t="inlineStr"/>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -25417,20 +25417,20 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>D | 748呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
         <is>
           <t>E | 769呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -25472,20 +25472,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>D | 748呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>E | 769呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -25527,20 +25527,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="24" t="inlineStr">
         <is>
           <t>D | 748呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>E | 769呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -25582,20 +25582,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>D | 748呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>E | 769呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -26686,34 +26686,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -12434,38 +12434,30 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H176" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I176" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="n">
+        <v>70497000</v>
+      </c>
+      <c r="I176" s="5" t="n">
+        <v>37800</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K176" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L176" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K176" s="5" t="n">
+        <v>70497000</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>37800</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
@@ -12474,7 +12466,7 @@
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18300,7 +18292,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -18310,12 +18302,12 @@
       </c>
       <c r="H267" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I267" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J267" s="3" t="inlineStr">
@@ -18325,12 +18317,12 @@
       </c>
       <c r="K267" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L267" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M267" s="3" t="inlineStr">
@@ -18340,7 +18332,7 @@
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23439,29 +23431,11 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23469,7 +23443,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23477,6 +23451,24 @@
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24237,44 +24229,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24958,7 +24950,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -24968,7 +24960,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25049,41 +25041,14 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 招标单位
@@ -25091,7 +25056,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25100,18 +25065,45 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 1865呎 (4+房)
-招标单位
--
-(在售)</t>
+$7050万
+$37,800/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -25834,27 +25826,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -26164,12 +26156,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>A | 1555呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -26686,34 +26678,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -18292,38 +18292,30 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H267" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I267" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H267" s="5" t="n">
+        <v>40430000</v>
+      </c>
+      <c r="I267" s="5" t="n">
+        <v>26000</v>
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K267" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L267" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K267" s="5" t="n">
+        <v>40430000</v>
+      </c>
+      <c r="L267" s="5" t="n">
+        <v>26000</v>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
@@ -18332,7 +18324,7 @@
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23431,11 +23423,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23443,7 +23453,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23451,24 +23461,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24229,44 +24221,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25041,14 +25033,41 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 招标单位
@@ -25056,7 +25075,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25064,33 +25083,6 @@
 (在售)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -25826,7 +25818,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -25836,7 +25828,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -26156,12 +26148,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 1555呎 (4+房)
-招标单位
--
-(在售)</t>
+$4043万
+$26,000/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -26678,34 +26670,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -18970,7 +18970,7 @@
         </is>
       </c>
       <c r="E278" s="4" t="n">
-        <v>1530</v>
+        <v>1473</v>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>37798000</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>24705</v>
+        <v>25661</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>37798000</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>24705</v>
+        <v>25661</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
@@ -23423,29 +23423,11 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23453,7 +23435,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23461,6 +23443,24 @@
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24221,44 +24221,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25033,41 +25033,14 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="21" t="inlineStr"/>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="21" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 招标单位
@@ -25075,7 +25048,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25083,6 +25056,33 @@
 (在售)</t>
         </is>
       </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -26275,9 +26275,9 @@
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>B | 1530呎 (4+房)
+          <t>B | 1473呎 (4+房)
 $3780万
-$24,705/呎
+$25,661/呎
 (26年-09月-17日)</t>
         </is>
       </c>
@@ -26670,34 +26670,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -18288,7 +18288,7 @@
         </is>
       </c>
       <c r="E267" s="4" t="n">
-        <v>1555</v>
+        <v>1498</v>
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>40430000</v>
       </c>
       <c r="I267" s="5" t="n">
-        <v>26000</v>
+        <v>26989</v>
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>40430000</v>
       </c>
       <c r="L267" s="5" t="n">
-        <v>26000</v>
+        <v>26989</v>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -26150,9 +26150,9 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>A | 1555呎 (4+房)
+          <t>A | 1498呎 (4+房)
 $4043万
-$26,000/呎
+$26,989/呎
 (26年-09月-28日)</t>
         </is>
       </c>
@@ -26278,7 +26278,7 @@
           <t>B | 1473呎 (4+房)
 $3780万
 $25,661/呎
-(26年-09月-17日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -26670,34 +26670,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -14654,34 +14654,34 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
-        <v>28197900</v>
+        <v>26506000</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>29342</v>
+        <v>27582</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K210" s="5" t="n">
-        <v>26506026</v>
+        <v>26506000</v>
       </c>
       <c r="L210" s="5" t="n">
         <v>27582</v>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N210" s="3" t="inlineStr">
@@ -24942,7 +24942,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -24952,7 +24952,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25448,12 +25448,12 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 961呎 (3房)
-$2820万
-$29,342/呎
-(在售)</t>
+$2651万
+$27,582/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -26670,34 +26670,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -12430,7 +12430,7 @@
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>1865</v>
+        <v>1788</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -12439,14 +12439,14 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
         <v>70497000</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>37800</v>
+        <v>39428</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>70497000</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>37800</v>
+        <v>39428</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
@@ -23423,11 +23423,29 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2780呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1276呎 (3房)
 $3228万
@@ -23435,7 +23453,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 1304呎 (3房)
 -
@@ -23443,24 +23461,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2780呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -24221,44 +24221,44 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 1272呎 (3房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2829呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>C | 1262呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2829呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1272呎 (3房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 1262呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="E7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
@@ -25033,14 +25033,41 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="21" t="inlineStr"/>
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="21" t="inlineStr"/>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>E | 765呎 (3房)
 招标单位
@@ -25048,7 +25075,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>F | 768呎 (3房)
 $1976万
@@ -25057,33 +25084,6 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2599呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2876呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-    </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
         <is>
@@ -25092,10 +25092,10 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 1865呎 (4+房)
+          <t>A | 1788呎 (4+房)
 $7050万
-$37,800/呎
-(26年-09月-22日)</t>
+$39,428/呎
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -26670,34 +26670,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -18297,7 +18297,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -26153,7 +26153,7 @@
           <t>A | 1498呎 (4+房)
 $4043万
 $26,989/呎
-(26年-09月-28日)</t>
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -26670,34 +26670,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">

--- a/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
+++ b/九龙-石硖尾-Beacon Peak 第1期/Beacon Peak 第1期_销控明细表.xlsx
@@ -14654,34 +14654,34 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
-        <v>26506000</v>
+        <v>28197900</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>27582</v>
+        <v>29342</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="K210" s="5" t="n">
-        <v>26506000</v>
+        <v>26506026</v>
       </c>
       <c r="L210" s="5" t="n">
         <v>27582</v>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N210" s="3" t="inlineStr">
@@ -24942,7 +24942,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -24952,7 +24952,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25448,12 +25448,12 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>C | 961呎 (3房)
-$2651万
-$27,582/呎
-(26年-10月-12日)</t>
+$2820万
+$29,342/呎
+(在售)</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -26670,34 +26670,34 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1545呎 (4+房)
+          <t>25&amp;26</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2493呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>25&amp;26</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 2493呎 (4+房)
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1545呎 (4+房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
